--- a/output/第10期計画_人口推計コーホート分析の妥当性検証.xlsx
+++ b/output/第10期計画_人口推計コーホート分析の妥当性検証.xlsx
@@ -92,7 +92,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +102,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -171,10 +171,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,10 +189,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -614,17 +614,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>式の組み方（東神楽町・美瑛町）</t>
+          <t>式の組み方（7項目の点検）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>85歳以上を分母とする開放区間の扱い、男女の区別、0〜4歳を子ども女性比により置くことはいずれも適合している。令和8年9月16日の点検で指摘した東神楽町の女の予測人口の件（5年前の男女計によっていたもの）は是正されている。</t>
+          <t>適合2項目・不適合3項目・要是正2項目である。**7項目のうち5項目に修正又は表記の是正を要する。**変化率（5〜9歳から85〜89歳まで）と合計の行は3町とも適合しており、令和8年9月16日の点検で指摘した東神楽町の女の予測人口の件（5年前の男女計によっていたもの）と「計」の行がない件は是正されている。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>適合</t>
+          <t>要是正</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>5年前の90歳以上を分母としている。開放区間であるから5年前の85歳以上を分母とする。この1点により率が男1.1039・女1.1026となり（開放区間では男0.4450・女0.5000）、65歳以上が令和8年度で406人過大に出る。連鎖により令和32年度の総人口が41,241人（実績8,695人の4.7倍）へ発散する。</t>
+          <t>5年前の90歳以上を分母としている。東神楽町・美瑛町は5年前の85歳以上である。令和8年度のシートでは率が男1.3684・女1.1471となり（一括すると男0.5065・女0.5217）、65歳以上が令和8年度で406人過大に出る。基準の組が実測である5つのシートのいずれでも東川町の率が1を超える。</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>95〜99歳・100歳以上の変化率（3町とも）</t>
+          <t>95〜99歳・100歳以上に90歳以上の率を流用（3町とも）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>90歳以上の率を3つの階級に流用している。基準年の100歳以上が次期に繰り越されないため、90歳以上の合計はおおむね保たれるが内訳が歪み、100歳以上が過大に出る。</t>
+          <t>90歳以上を3つの階級に分けたまま、1つの率を3つに用いている。基準年の100歳以上が次期に繰り越されない。**3つの階級を残すのであれば階級ごとに分母を採る**（02シートの下段に式を示した）。この形に改めると、2の分母の件と東川町の女の100歳以上が男女計の行を参照している件も同時に解消する。</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>正しく組み直した場合の水準</t>
+          <t>令和17年度以降のシートが前のシートを参照しない</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>65歳以上（3町計）は令和7年度の実績9,176人に対し令和12年度9,081人・令和22年度9,095人・令和32年度8,682人で横ばいとなり、案C（令和12年度9,211人・令和22年度9,491人・令和32年度9,127人）との開きは3〜4％以内で向きも一致する。</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>9つのシートの式4,017件のうち、他のシートを参照するものは0件である。令和17年度以降の基準の組は、前のシートの予測値を**数値として貼り付けたもの**である。**上流の式を直しても令和17年度から令和32年度の値は追随しない。**令和12年度を再計算したうえで、令和17年度以降を順に作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>不適合</t>
         </is>
       </c>
     </row>
@@ -702,17 +702,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>「令和5年推計を元にした補正（大雪）」の男女</t>
+          <t>正しく組み直した場合の水準</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>（2）女は（1）男と全ての欄が同一であり、（3）合計は男＋女にならない。女の値が入っていない。同じファイルの「被保険者数（補正後）補正率2区分」には男女別の値がある。</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>不適合</t>
+          <t>65歳以上（3町計）は令和7年度の実績9,176人に対し令和12年度9,081人・令和22年度9,095人・令和32年度8,682人で横ばいとなり、案C（令和12年度9,211人・令和22年度9,491人・令和32年度9,127人）との開きは▲4.9％から▲1.4％である。**保険料への影響は、年齢階級別の認定率・給付費・基金等を反映した保険料の算定により別に確かめる。**</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
         </is>
       </c>
     </row>
@@ -724,17 +724,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>時点の表示</t>
+          <t>2つの補正値の系列で第1号被保険者数の総数が違う</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>各シートは5年の変化率を基準年に乗じているため、得られる値は基準年の5年後の1月1日である。「令和N年」は年度として読めば整合するが、併記されている「20XX年」は1年ずれている。時点の注記は資料の中に3通りある。</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>要是正</t>
+          <t>「令和5年推計を元にした補正」の（3）合計と「被保険者数（補正後）補正率2区分」の男女の和は、令和11年度9,107人対9,094人・令和22年度9,375人対9,430人で、最大55人の差がある（令和22年度）。**別のロジックによる2つの系列であり、総数と男女別を混ぜて用いられない。**（2）女は（1）男と全ての欄が同一であり女の値が入っていない。</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>不適合</t>
         </is>
       </c>
     </row>
@@ -746,23 +746,67 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>時点の表示</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>各シートは5年の変化率を基準年に乗じているため、得られる値は基準年の5年後の1月1日である。令和8年度のシートは令和4年1月1日に乗じているため**令和9年1月1日現在**の値となる。「令和N年」は年度として読めば整合するが、併記されている「20XX年」は1年ずれている。時点の注記は資料の中に3通りある。</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>要是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>受領ファイルの文字の誤り・人口ビジョンの読み方</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>調査の名称・推計の名称ほか4件の文字の誤りがある（03シート）。また、美瑛町の人口ビジョンに置かれている1年ごとの値は、基準年（2020年・2030年・2040年・2060年）の値を**線形に補間したもの**であり、年次ごとに推計されたものではない。</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>要是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>スケジュールの記載</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>パブリックコメントの期間（令和9年1月・ウェブで2週間）と令和9年2月以降の会議の日程が分かった。当方の月別工程に取り込んだ（確認事項No.19）。</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>本検証は、受領ファイルに置かれている住民基本台帳の実績値（各年1月1日現在。10時点×3町×男女×5歳階級21区分）と、各シートの予測人口の値のみを用いています。
 当方の組み直しは、受領ファイルと同じ基準の組を用い、分母の採り方だけを改めたものです。基準の組を変えずに比べることで、差が分母の採り方によるものであることを示しています。</t>
@@ -773,7 +817,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1137,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1202,12 +1246,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>東川町の90歳以上の変化率の分母</t>
+          <t>90歳以上の3つの階級の式を3町共通の階級別の式に改める</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>SUM(W31:Y31) を SUM(V31:Y31) に改める（男・女×9シート＝18か所）。この1か所で発散は止まる。</t>
+          <t>90〜94歳＝5年前の85〜89歳、95〜99歳＝5年前の90〜94歳、100歳以上＝5年前の（95〜99歳＋100歳以上）を分母とする。予測は 90〜94歳＝基準年の85〜89歳×率、100歳以上＝基準年の（95〜99歳＋100歳以上）×率。女の行は女の行を参照する（東川町の Y51＝X36*W41 を X35*W41 に）。これにより東川町の分母の件・率の流用の件・女の参照先の件が同時に解消する。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1229,12 +1273,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>東川町の女の100歳以上の参照</t>
+          <t>東川町の0〜4歳の分母を予測年の女20〜39歳に改める</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Y51の =X36*W41 を =X35*W41 に改める（9シート）。</t>
+          <t>E50・E51を =SUM(I51:L51)*E40 の形に改め、3町でそろえる。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1256,12 +1300,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>95〜99歳・100歳以上の変化率（3町とも）</t>
+          <t>令和12年度のシートを再計算する</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>階級ごとに分母を採る。95〜99歳＝5年前の90〜94歳、100歳以上＝5年前の（95〜99歳＋100歳以上）。</t>
+          <t>1・2の式に改めたうえで、住民基本台帳の実測2時点を基準の組として計算し直す。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1283,12 +1327,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>「令和5年推計を元にした補正」の女</t>
+          <t>令和17年度以降を令和12年度から順に作り直す</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>「被保険者数（補正後）補正率2区分」の男女別の値を用いる。（3）合計はそのまま用いることができる。</t>
+          <t>**令和17年度以降のシートは前のシートを参照していないため、1・2の式を直しても追随しない。**令和12年度 → 令和17年度 → 令和22年度 → 令和27年度 → 令和32年度の順に、前のシートの予測値を次のシートの基準の組に入れ直す（又はシート間を式でつなぐ）。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1305,17 +1349,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>0〜4歳の分母を3町でそろえる</t>
+          <t>見える化システムの入力の6階級に集約する</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>東川町を予測年の女20〜39歳に改める。</t>
+          <t>65〜69歳・70〜74歳・75〜79歳・80〜84歳・85〜89歳・90歳以上（男女別）にまとめる。90歳以上は3つの階級の和とする。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1332,22 +1376,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>時点の表示</t>
+          <t>案C・社人研推計を補正した値と突き合わせる</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>見出しを「令和N年度（20XX+1年1月1日現在）」の形に統一する。注記を1つにそろえる。令和32年シートの見出しを改める。</t>
+          <t>総数・男女別・6階級を同じ系列から作り、どれを正式に採る値とするかを決める（2つの補正値の系列で総数が一致しない。確認事項No.174）。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>受領ファイルの作成者</t>
+          <t>受領ファイルの作成者・受託者</t>
         </is>
       </c>
     </row>
@@ -1359,22 +1403,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>合計特殊出生率の表示</t>
+          <t>保険料推計への影響を確かめる</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>「子ども女性比×4（合計特殊出生率の目安）」と記す。</t>
+          <t>性別・年齢階級別・要介護度別の認定率を乗じて認定者数を求め、見込量・給付費・保険料まで通して算定し直す。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>受領ファイルの作成者</t>
+          <t>受託者</t>
         </is>
       </c>
     </row>
@@ -1386,17 +1430,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>東川町のシートのデータ元のURL</t>
+          <t>時点の表示</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>東川町の計画のURLに改める。</t>
+          <t>見出しを「令和N年度（20XX+1年1月1日現在）」の形に統一する。注記を1つにそろえる。令和32年シートの見出しを改める。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1413,22 +1457,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>中</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>スケジュールの取込み</t>
+          <t>「令和5年推計を元にした補正」の女</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの期間と令和9年2月以降の会議の日程を月別工程に取り込んだ。</t>
+          <t>「被保険者数（補正後）補正率2区分」の男女別の値を用いる。（3）合計はそのまま用いることができる。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>受託者（実施済み）</t>
+          <t>受領ファイルの作成者</t>
         </is>
       </c>
     </row>
@@ -1440,22 +1484,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>低</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>進捗と今後の確認事項の加筆・削除の取込み</t>
+          <t>合計特殊出生率の表示・文字の誤り・データ元のURL</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>表紙の表記と資料の所在を指す記述3件を改めた。</t>
+          <t>「子ども女性比×4（合計特殊出生率の目安）」と記す。文字の誤り4件（03シート）を改める。東川町のシートのデータ元を東川町の計画のURLに改める。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>受託者（実施済み）</t>
+          <t>受領ファイルの作成者</t>
         </is>
       </c>
     </row>
@@ -1472,25 +1516,80 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t>スケジュールの取込み</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの期間と令和9年2月以降の会議の日程を月別工程に取り込んだ。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>受託者（実施済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>進捗と今後の確認事項の加筆・削除の取込み</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>表紙の表記と資料の所在を指す記述3件を改めた。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>受託者（実施済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
           <t>コーホート変化率法の計算の共通化</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>変化率と5年進めの計算を1か所にまとめ、令和8年9月16日の点検と本検証の双方が同じ計算を用いる形にした。</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>受託者（実施済み）</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>注）推計の方法を案Cから改めるかどうかは確認事項No.153であり、既定値は「令和8年9月10日のご了承のとおり案Cのままとする」です。本検証は、コーホート変化率法を正しく組み直しても案Cと3〜4％以内で一致することを示すものであり、いずれを採っても保険料の水準は大きく変わりません。
+    <row r="18"/>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>注）1から7は順に行う必要があります。**上流の式を直しても、令和17年度以降の予測値は固定の数値として置かれているため追随しません。**「18か所を直して終わり」とはなりません。
+推計の方法を案Cから改めるかどうかは確認事項No.153であり、既定値は「令和8年9月10日のご了承のとおり案Cのままとする」です。本検証は、コーホート変化率法を正しく組み直すと65歳以上人口が案C比▲4.9％から▲1.4％になることを示すものです。保険料への影響は、年齢階級別の認定率・給付費・基金等を反映した算定により別に確かめます。
 将来推計を町別に掲げることは令和8年9月10日のご了承（町別は現況のみ本文に加え、将来推計は3町計の案Cのままとする）と食い違います（確認事項No.152）。</t>
         </is>
       </c>
@@ -1498,8 +1597,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1511,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1582,7 +1681,7 @@
           <t>7件</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1607,7 +1706,7 @@
           <t>3件（90歳以上の変化率の分母／95〜99歳・100歳以上の変化率／男女の区別）</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1619,20 +1718,20 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>東川町の90歳以上の変化率（令和12年シート）</t>
+          <t>東川町の90歳以上の変化率</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領＝基準年の90歳以上÷5年前の90歳以上／開放区間＝基準年の90歳以上÷5年前の85歳以上</t>
+          <t>受領＝基準年の90歳以上÷5年前の90歳以上（東川町）／一括＝基準年の90歳以上÷5年前の85歳以上</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>男 受領1.1039・開放区間0.4450／女 受領1.1026・開放区間0.5000</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+          <t>令和8年度のシートで 男 受領1.3684・一括0.5065／女 受領1.1471・一括0.5217。基準の組が実測である5つのシートのうち、率が1を超えるのは10件ですべて東川町である</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1654,10 +1753,10 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>いずれも0.3から0.7の間にある（1を超えない）</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+          <t>基準の組が実測である5つのシートのいずれも1を超えない</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1665,24 +1764,24 @@
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>東川町の65歳以上（令和8年度）</t>
+          <t>令和17年度以降のシートの基準の組</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>受領値と、同じ基準の組で当方の置き方により求めた値の差</t>
+          <t>9つのシートの式のうち他のシートを参照するものの件数</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>受領3075.4人・当方2669.4人（差▲406.0人）</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+          <t>0件（基準の組は予測値を数値として貼り付けたものである）</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1690,24 +1789,24 @@
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>東川町の総人口（令和32年度）の発散</t>
+          <t>2つの補正値の系列の第1号被保険者数</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>受領値と住民基本台帳の実績（令和8年1月1日8,695人）の比</t>
+          <t>「令和5年推計を元にした補正」の（3）合計と「被保険者数（補正後）補正率2区分」の男女の和を年度ごとに比べる</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>受領41241人（実績の4.74倍）</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+          <t>差が最も大きいのは令和22年度（9,375人対9,430人・＋55人）</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1715,24 +1814,24 @@
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>東神楽町の65歳以上（令和12年度）</t>
+          <t>東川町の65歳以上（令和8年度）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>受領値と当方の組み直しの差の割合</t>
+          <t>受領値と、同じ基準の組で当方の置き方により求めた値の差</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>受領2998.6人・当方2992.8人（▲0.19％）</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+          <t>受領3075.4人・当方2669.4人（差▲406.0人）</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1740,24 +1839,24 @@
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>美瑛町の65歳以上（令和12年度）</t>
+          <t>東川町の総人口（令和32年度）の発散</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>受領値と当方の組み直しの差の割合</t>
+          <t>受領値と住民基本台帳の実績（令和8年1月1日8,695人）の比</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>受領3441.0人・当方3431.3人（▲0.28％）</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+          <t>受領41241人（実績の4.74倍）</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1765,24 +1864,24 @@
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>当方の連鎖の基準年（令和7年度）</t>
+          <t>東神楽町の65歳以上（令和12年度）</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>住民基本台帳 令和8年1月1日現在の3町計の総人口</t>
+          <t>受領値と当方の組み直しの差の割合</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>27,498人</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+          <t>受領2998.6人・当方2992.8人（▲0.19％）</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1790,24 +1889,24 @@
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>当方の連鎖と案Cの65歳以上の対比（令和22年度）</t>
+          <t>美瑛町の65歳以上（令和12年度）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>3町計の65歳以上と案Cの第1号被保険者数</t>
+          <t>受領値と当方の組み直しの差の割合</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>当方の連鎖9095人・案C9491人（▲4.2％）</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+          <t>受領3441.0人・当方3431.3人（▲0.28％）</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1815,24 +1914,24 @@
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>当方の連鎖の65歳以上が横ばいであること</t>
+          <t>当方の連鎖の基準年（令和7年度）</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>3町計の65歳以上が全年度で9,100人±500人の範囲にあること</t>
+          <t>住民基本台帳 令和8年1月1日現在の3町計の総人口</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>令和7年度 9176人／令和12年度 9081人／令和17年度 8982人／令和22年度 9095人／令和27年度 8933人／令和32年度 8682人</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+          <t>27,498人</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1840,24 +1939,24 @@
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>「令和5年推計を元にした補正」の男女</t>
+          <t>当方の連鎖と案Cの65歳以上の対比（令和22年度）</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>（1）男と（2）女の全ての欄を比べ、（3）合計が男＋女になるかを見る</t>
+          <t>3町計の65歳以上と案Cの第1号被保険者数</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>男と女は全ての欄が同一／合計が男＋女にならない項目 9件</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+          <t>当方の連鎖9095人・案C9491人（▲4.2％）</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1865,24 +1964,24 @@
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>被保険者数（補正後）補正率2区分の第1号被保険者数</t>
+          <t>当方の連鎖の65歳以上が横ばいであること</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>男女の65〜69歳から90歳以上までの和</t>
+          <t>3町計の65歳以上が全年度で9,100人±500人の範囲にあること</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>令和6年度9,153人・令和11年度9,094人・令和22年度9,430人</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+          <t>令和7年度 9176人／令和12年度 9081人／令和17年度 8982人／令和22年度 9095人／令和27年度 8933人／令和32年度 8682人</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1890,24 +1989,24 @@
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>国の「推計人口と第1号被保険者数の比較」</t>
+          <t>「令和5年推計を元にした補正」の男女</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>差分の対推計人口比が最も大きい区分</t>
+          <t>（1）男と（2）女の全ての欄を比べ、（3）合計が男＋女になるかを見る</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>85歳以上 9.2％（推計人口2,167人・被保険者数1,967人）</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+          <t>男と女は全ての欄が同一／合計が男＋女にならない項目 9件</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1915,24 +2014,24 @@
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>構成3町の人口ビジョン・総合計画による総人口</t>
+          <t>被保険者数（補正後）補正率2区分の第1号被保険者数</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>3町の値の和（2030年・2040年）</t>
+          <t>男女の65〜69歳から90歳以上までの和</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>2030年26,881人・2040年25,263人</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
+          <t>令和6年度9,153人・令和11年度9,094人・令和22年度9,430人</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1940,24 +2039,24 @@
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>社人研推計（令和5年推計）による3町計の総人口</t>
+          <t>国の「推計人口と第1号被保険者数の比較」</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>受領ファイルの「自然推計」の行</t>
+          <t>差分の対推計人口比が最も大きい区分</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>R6 27,303人・R22 23,582人・R32 21,058人</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
+          <t>85歳以上 9.2％（推計人口2,167人・被保険者数1,967人）</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1965,24 +2064,24 @@
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>受領ファイルのスケジュールの件数</t>
+          <t>構成3町の人口ビジョン・総合計画による総人口</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>日程が明記されている事項</t>
+          <t>3町の値の和（2030年・2040年）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>8件（令和9年2月19日・3月2日・3月3日・3月23日を含む）</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+          <t>2030年26,881人・2040年25,263人</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1990,24 +2089,24 @@
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>見つけた誤りの件数</t>
+          <t>社人研推計（令和5年推計）による3町計の総人口</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>GOYMIの件数</t>
+          <t>受領ファイルの「自然推計」の行</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>10件</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+          <t>R6 27,303人・R22 23,582人・R32 21,058人</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2015,24 +2114,99 @@
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>受領ファイルのスケジュールの件数</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>日程が明記されている事項</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>8件（令和9年2月19日・3月2日・3月3日・3月23日を含む）</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>見つけた誤りの件数</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>GOYMIの件数</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>11件</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>文字の誤りの件数</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>GOJIの件数と03シートの掲げ方</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>4件（調査の名称・推計の名称・診療科の名称・読み取れない記載）</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>禁止表現が本表にないこと</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>禁止表現5件を全てのセルで探す</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>0件</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2238,7 +2412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2307,17 +2481,17 @@
           <t>基準年の階級a ÷ 5年前の階級(a−5歳)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2339,7 +2513,7 @@
           <t>開放区間であるため5年前の85歳以上を分母とする</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2349,7 +2523,7 @@
           <t>不適合</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2403,17 +2577,17 @@
           <t>子ども女性比（基準年の0〜4歳÷基準年の20〜39歳女性）を予測年の20〜39歳女性に乗じる</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>要是正</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2435,7 +2609,7 @@
           <t>女の予測人口は5年前の女に女の変化率を乗じる</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2445,7 +2619,7 @@
           <t>不適合</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2467,17 +2641,17 @@
           <t>予測人口の男女計と町の合計が全ての階級で立つ</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2499,17 +2673,17 @@
           <t>子ども女性比×4は合計特殊出生率の目安であり合計特殊出生率ではない</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>要是正</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>要是正</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>要是正</t>
         </is>
@@ -2524,7 +2698,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>【90歳以上の変化率（令和12年シート・東川町）】</t>
+          <t>【90歳以上の変化率（令和8年度のシート・東川町）】</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2730,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>開放区間の率</t>
+          <t>一括の率</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2741,22 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>1.1039</t>
+          <t>1.3684</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>0.4450</t>
+          <t>0.5065</t>
         </is>
       </c>
     </row>
@@ -2593,29 +2767,29 @@
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>344</v>
+        <v>299</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>1.1026</t>
+          <t>1.1471</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.5217</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>注）開放区間の率は、5年前に85歳以上であった方が5年後に90歳以上になることによります。分母を5年前の90歳以上に採ると、その間に90歳に達した方を分母に数えないまま分子に数えることになるため、率が1を超えます。</t>
+          <t>注）基準の組は平成29年1月1日と令和4年1月1日です。分母を5年前の90歳以上に採ると、その間に90歳に達した方を分母に数えないまま分子に数えることになるため、率が1を超えます。</t>
         </is>
       </c>
     </row>
@@ -2623,153 +2797,399 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>【式の欄の位置（令和12年シートによる）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>町</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>90歳以上の率</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>0〜4歳の分母</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+          <t>【90歳以上を3つの階級のまま残す場合の式（これを推す）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>受領ファイルは90〜94歳・95〜99歳・100歳以上の3つの階級を残しています。この形のまま用いるのであれば、**1つの率を3つに流用せず、階級ごとに分母を採る**のが整合的です。下表は東川町の欄の位置によるものです（令和12年シートの行番号。他のシート・他の町も同じ構造です）。
+この形に改めると、90歳以上の分母の件（東川町）と女の100歳以上が男女計の行を参照している件も同時に解消します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>階級</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>変化率（男）</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>変化率（女）</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>予測人口（男）</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>予測人口（女）</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>令和8年度の率（東川町・男／女）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>90〜94歳</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>W40 = W34/V31</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>W41 = W35/V32</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>W50 = V34*W40</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>W51 = V35*W41</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>0.6082 ／ 0.7117</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>95〜99歳</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>X40 = X34/W31</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>X41 = X35/W32</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>X50 = W34*X40</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>X51 = W35*X41</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>0.3556 ／ 0.3524</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>100歳以上</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Y40 = Y34/SUM(X31:Y31)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Y41 = Y35/SUM(X32:Y32)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Y50 = SUM(X34:Y34)*Y40</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Y51 = SUM(X35:Y35)*Y41</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>0.2500 ／ 0.0968</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>（参考）90歳以上を1つの開放区間とする場合</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>W40 = SUM(W34:Y34)/SUM(V31:Y31)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>同（行32）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>W50 = SUM(V34:Y34)*W40</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>同（行35）</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>0.5065 ／ 0.5217</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>注）階級ごとに分母を採る場合、100歳以上は開放区間であるため5年前の95〜99歳と100歳以上の和を分母とし、予測は基準年の95〜99歳と100歳以上の和に率を乗じます。これにより基準年の100歳以上が次期へ繰り越されます。
+当方の組み直し（04・05シート）はこの階級別の方式によっています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>【90歳以上の変化率（受領ファイルの採り方。3町×5つのシート）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>シート</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>東神楽 男／女</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>東川 男／女</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>美瑛 男／女</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>1を超える件数</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>東神楽</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>SUM(W7:Y7)/SUM(V4:Y4)</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>SUM(I24:L24)（予測年の女）</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>X7*W14・X8*W15</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>分母が5年前の85歳以上（V列＝85〜89歳からY列＝100歳以上まで）である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>東川</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>SUM(W34:Y34)/SUM(W31:Y31)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>SUM(I35:L35)（基準年の女）</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>X34*W40・X36*W41</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>令和8年（2026年）
+→ 令和8年度（令和9年1月1日現在）</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>0.4308 ／ 0.5467</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>1.3684 ／ 1.1471</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>0.4249 ／ 0.5204</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>不適合</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>分母がW列（90〜94歳）から始まる。女の100歳以上はX36（男女計の行）を参照している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>美瑛</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>SUM(W62:Y62)/SUM(V59:Y59)</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>SUM(I78:L78)（予測年の女）</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>X62*W68・X63*W69</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>分母が5年前の85歳以上である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>注）欄の位置は令和12年シートのものです。9つの年次シートはいずれも同じ式であり、行の番号だけが町のかたまりごとに異なります。</t>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>令和9年（2027年）
+→ 令和9年度（令和10年1月1日現在）</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>0.4054 ／ 0.5172</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>1.3387 ／ 1.1176</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>0.4023 ／ 0.5473</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>不適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>令和10年（2028）
+→ 令和10年度（令和11年1月1日現在）</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>0.3885 ／ 0.4595</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>1.0132 ／ 1.1986</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>0.4183 ／ 0.5149</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>不適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>令和11年（2029）
+→ 令和11年度（令和12年1月1日現在）</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>0.4048 ／ 0.4702</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>1.1014 ／ 1.1391</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>0.4286 ／ 0.5114</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>不適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>令和12年（2030）
+→ 令和12年度（令和13年1月1日現在）</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>0.4375 ／ 0.5000</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>1.1039 ／ 1.1026</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>0.3948 ／ 0.5197</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>不適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>注）基準の組が住民基本台帳の実測である5つのシートについて求めました。令和17年度以降は基準の組が予測値であるため別に掲げていません。**東川町は5つのシートのいずれでも率が1を超えます。**高齢の階級の変化率が1を超えることは、転入がなければ起こりません（分母の採り方を疑う目安です）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2781,7 +3201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2841,22 +3261,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>東川町の90歳以上の変化率の分母</t>
+          <t>90歳以上の3つの階級の変化率（東川町の分母・率の流用・女の参照先）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>開放区間であるのに5年前の90歳以上を分母としている。東神楽町・美瑛町は5年前の85歳以上としており、3町でそろっていない。</t>
+          <t>次の3つはいずれも90歳以上の3つの階級の置き方によるものであり、階級ごとに分母を採る形に改めれば同時に解消します。①東川町のみ開放区間の分母を5年前の90歳以上としている（他の2町は5年前の85歳以上）。②3町とも90歳以上の率を95〜99歳・100歳以上に流用している。③東川町の女の100歳以上が男女計の行を参照している（Y51＝X36*W41）。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>東川町の65歳以上が令和8年度で406人（＋15.2％）過大。連鎖により令和22年度12,642人・令和32年度34,573人となり、3町計の総人口が令和32年度53,652人（実績27,498人の1.95倍）になる。</t>
+          <t>①により東川町の65歳以上が令和8年度で406人（＋15.2％）過大となり、連鎖して令和22年度12,642人・令和32年度34,573人、3町計の総人口が令和32年度53,652人（実績27,498人の1.95倍）になる。②は90歳以上の合計をおおむね保つが内訳が歪み、基準年の100歳以上が次期に繰り越されない。③は女の100歳以上が男女計から求められる。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>分母を SUM(V31:Y31)（5年前の85歳以上）に改める。男・女の2か所×9シート＝18か所。</t>
+          <t>3町共通の階級別の式に改める（02シートの表のとおり）。90〜94歳＝5年前の85〜89歳、95〜99歳＝5年前の90〜94歳、100歳以上＝5年前の（95〜99歳＋100歳以上）を分母とし、予測は 90〜94歳＝基準年の85〜89歳×率、100歳以上＝基準年の（95〜99歳＋100歳以上）×率とする。女の行は女の行（行32・行35）を参照する。</t>
         </is>
       </c>
     </row>
@@ -2868,22 +3288,22 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>95〜99歳・100歳以上に90歳以上の率を流用（3町とも）</t>
+          <t>令和17年度以降のシートが前のシートの計算結果を参照しない</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>X列＝W7*W14、Y列＝X7*W14 のように、90歳以上の率を3つの階級に用いている。基準年の100歳以上（Y列）が次期に繰り越されない。</t>
+          <t>9つのシートの式のうち他のシートを参照するものは0件であり、令和17年度以降のシートは基準の組（5年前・10年前の人口）を数値として持っています。シートは式でつながっておらず、前のシートの予測値を貼り付けたものです。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>90歳以上の合計はおおむね保たれるが、内訳が歪む。100歳以上が過大に、90〜94歳が過小に出る。介護保険の算定に用いる85歳以上の合計への影響は小さい。</t>
+          <t>**①の式を直しても令和17年度から令和32年度の値は追随しません。**基準の組の数値そのものが①の誤りを含んだ予測値であるため、上流（令和12年度）を直した後に、令和17年度以降を順に作り直す必要があります。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>階級ごとに分母を採る。95〜99歳は5年前の90〜94歳、100歳以上は5年前の95〜99歳と100歳以上の和を分母とする。</t>
+          <t>①の是正の後、令和12年度 → 令和17年度 → 令和22年度 → 令和27年度 → 令和32年度の順に、前のシートの予測値を次のシートの基準の組に入れ直す（又はシート間を式でつなぐ）。手順は10シートのとおりです。</t>
         </is>
       </c>
     </row>
@@ -2895,22 +3315,23 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>東川町の女の100歳以上が男女計の行を参照</t>
+          <t>0〜4歳の分母が3町でそろっていない</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Y51の式が =X36*W41 であり、X36は男女計の行である。女の行はX35である。</t>
+          <t>東神楽町・美瑛町は予測年の女20〜39歳、東川町は基準年の女20〜39歳を分母としている。</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>女の100歳以上が男女計の95〜99歳から求められる。他の2町は正しく女の行を参照している。</t>
-        </is>
-      </c>
-      <c r="E7" s="5">
-        <f>X35*W41 に改める。9シート。</f>
-        <v/>
+          <t>東川町の0〜4歳が他の2町より大きく出る。子ども女性比は同じ年の比であるため、予測年の女に乗じるのが式の定義に沿う。65歳以上の値には及ばない。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>東川町のE50・E51を =SUM(I51:L51)*E40 の形に改める（予測年の女の行を参照する）。</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="74" customHeight="1">
@@ -2921,22 +3342,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0〜4歳の分母が3町でそろっていない</t>
+          <t>2つの補正値の系列で第1号被保険者数の総数が違う</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>東神楽町・美瑛町は予測年の女20〜39歳、東川町は基準年の女20〜39歳を分母としている。</t>
+          <t>同じファイルの中に、社人研推計を補正した第1号被保険者数の系列が2つあります。「令和5年推計を元にした補正（大雪）」の（3）合計と、「被保険者数（補正後）補正率2区分」の男女の和です。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>東川町の0〜4歳が他の2町より大きく出る。子ども女性比は同じ年の比であるため、予測年の女に乗じるのが式の定義に沿う。</t>
+          <t>年度ごとの差は▲14人から＋55人で、最も大きいのは令和22年度（9,375人対9,430人・＋55人）。見える化システムの入力は総数と男女別6階級の両方を求めるため、別の系列から採ると画面の中で計が合わなくなる。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>東川町のE50・E51を =SUM(I51:L51)*E40 の形に改める（予測年の女の行を参照する）。</t>
+          <t>どちらを正式に採る値とするかを先に決め、総数・男女別・6階級を同じ系列から作る。→ 確認事項No.174として起票した。</t>
         </is>
       </c>
     </row>
@@ -2948,22 +3369,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>時点の表示が1年ずれている</t>
+          <t>「令和5年推計を元にした補正（大雪）」の女</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>5年の変化率を基準年に乗じているため、得られる値は基準年の5年後の1月1日である。令和8年シートは2022年1月1日に乗じているため2027年1月1日となる。</t>
+          <t>（2）女の9項目×11年度の全ての欄が（1）男と同一であり、（3）合計は男＋女にならない。</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>「令和N年」は年度として読めば整合する。併記されている「20XX年」は1年ずれている。時点の注記は3通りあり、資料の中で統一されていない。</t>
+          <t>女の値が入っていない。85歳以上は女が男の約1.8倍であるため、男女別に用いると実態と大きく異なる。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>見出しを「令和N年度（20XX+1年1月1日現在）」の形に統一する。注記も1つにそろえる。</t>
+          <t>同じファイルの「被保険者数（補正後）補正率2区分」の男女別の値を用いる。（3）合計はそのまま用いることができる。</t>
         </is>
       </c>
     </row>
@@ -2975,22 +3396,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>令和32年シートの予測の見出し</t>
+          <t>時点の表示が1年ずれている</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>基準の組は令和22年度と令和27年度の推計値であり、予測は令和32年度であるが、見出しが「2045年（令和27年）」のままになっている。</t>
+          <t>5年の変化率を基準年に乗じているため、得られる値は基準年の5年後の1月1日である。令和8年シートは2022年1月1日に乗じているため2027年1月1日となる。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>値そのものには影響しない。見出しだけの誤りである。</t>
+          <t>「令和N年」は年度として読めば整合する。併記されている「20XX年」は1年ずれている。時点の注記は3通りあり、資料の中で統一されていない。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>「2050年（令和32年）」に改める。</t>
+          <t>見出しを「令和N年度（20XX+1年1月1日現在）」の形に統一する。注記も1つにそろえる。</t>
         </is>
       </c>
     </row>
@@ -3002,22 +3423,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>令和8年シートの注記の年</t>
+          <t>令和32年シートの予測の見出し</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>注記が「2016年のデータと2021年のデータ」としているが、実際に用いているのは2017年1月1日と2022年1月1日である。</t>
+          <t>基準の組は令和22年度と令和27年度の推計値であり、予測は令和32年度であるが、見出しが「2045年（令和27年）」のままになっている。</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>値そのものには影響しない。ただし1月1日の値を前年のものとして扱う箇所と当年のものとして扱う箇所が混在する原因となっている。</t>
+          <t>値そのものには影響しない。見出しだけの誤りである。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>「2017年1月1日現在と2022年1月1日現在」に改める。</t>
+          <t>「2050年（令和32年）」に改める。</t>
         </is>
       </c>
     </row>
@@ -3029,22 +3450,22 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>「令和5年推計を元にした補正（大雪）」の女</t>
+          <t>令和8年シートの注記の年</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>（2）女の9項目×11年度の全ての欄が（1）男と同一であり、（3）合計は男＋女にならない。</t>
+          <t>注記が「2016年のデータと2021年のデータ」としているが、実際に用いているのは2017年1月1日と2022年1月1日である。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>女の値が入っていない。85歳以上は女が男の約1.8倍であるため、男女別に用いると実態と大きく異なる。</t>
+          <t>値そのものには影響しない。ただし1月1日の値を前年のものとして扱う箇所と当年のものとして扱う箇所が混在する原因となっている。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>同じファイルの「被保険者数（補正後）補正率2区分」の男女別の値を用いる。（3）合計はそのまま用いることができる。</t>
+          <t>「2017年1月1日現在と2022年1月1日現在」に改める。</t>
         </is>
       </c>
     </row>
@@ -3099,6 +3520,33 @@
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>東川町の計画のURLに改める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="74" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>文字の誤り4件</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>スケジュールのシート「IAGES調査」／「令和5年推計を元にした補正」の表題「日本の地域別修礼推計人口」／要約シートの検討事項「歯科医問う」／スケジュールのシートの備考「意見は寧」</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>いずれも値には影響しない。調査の名称・推計の名称は外部にお示しする資料に用いるため、正しい表記に改める必要がある。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>「JAGES調査」／「日本の地域別将来推計人口」／「歯科医師等」／「［要確認］」</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3644,8 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>令和8年（2026年）（令和8年度）</t>
+          <t>令和8年（2026年）
+→ 令和8年度（令和9年1月1日現在）</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -3234,7 +3683,7 @@
           <t>▲2.9</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3243,7 +3692,8 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>令和8年（2026年）（令和8年度）</t>
+          <t>令和8年（2026年）
+→ 令和8年度（令和9年1月1日現在）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -3290,7 +3740,8 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>令和8年（2026年）（令和8年度）</t>
+          <t>令和8年（2026年）
+→ 令和8年度（令和9年1月1日現在）</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -3328,7 +3779,7 @@
           <t>＋4.2</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3337,7 +3788,8 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>令和9年（2027年）（令和9年度）</t>
+          <t>令和9年（2027年）
+→ 令和9年度（令和10年1月1日現在）</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -3375,7 +3827,7 @@
           <t>▲1.9</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3384,7 +3836,8 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>令和9年（2027年）（令和9年度）</t>
+          <t>令和9年（2027年）
+→ 令和9年度（令和10年1月1日現在）</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -3431,7 +3884,8 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>令和9年（2027年）（令和9年度）</t>
+          <t>令和9年（2027年）
+→ 令和9年度（令和10年1月1日現在）</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -3469,7 +3923,7 @@
           <t>▲4.8</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3478,7 +3932,8 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>令和10年（2028）（令和10年度）</t>
+          <t>令和10年（2028）
+→ 令和10年度（令和11年1月1日現在）</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -3516,7 +3971,7 @@
           <t>▲0.2</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3525,7 +3980,8 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>令和10年（2028）（令和10年度）</t>
+          <t>令和10年（2028）
+→ 令和10年度（令和11年1月1日現在）</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -3572,7 +4028,8 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>令和10年（2028）（令和10年度）</t>
+          <t>令和10年（2028）
+→ 令和10年度（令和11年1月1日現在）</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -3610,7 +4067,7 @@
           <t>▲0.9</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3619,7 +4076,8 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>令和11年（2029）（令和11年度）</t>
+          <t>令和11年（2029）
+→ 令和11年度（令和12年1月1日現在）</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -3657,7 +4115,7 @@
           <t>▲4.2</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3666,7 +4124,8 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>令和11年（2029）（令和11年度）</t>
+          <t>令和11年（2029）
+→ 令和11年度（令和12年1月1日現在）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -3713,7 +4172,8 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>令和11年（2029）（令和11年度）</t>
+          <t>令和11年（2029）
+→ 令和11年度（令和12年1月1日現在）</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -3751,7 +4211,7 @@
           <t>▲8.6</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3760,7 +4220,8 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>令和12年（2030）（令和12年度）</t>
+          <t>令和12年（2030）
+→ 令和12年度（令和13年1月1日現在）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3798,7 +4259,7 @@
           <t>▲5.8</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3807,7 +4268,8 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>令和12年（2030）（令和12年度）</t>
+          <t>令和12年（2030）
+→ 令和12年度（令和13年1月1日現在）</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3854,7 +4316,8 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>令和12年（2030）（令和12年度）</t>
+          <t>令和12年（2030）
+→ 令和12年度（令和13年1月1日現在）</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3892,7 +4355,7 @@
           <t>▲9.7</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3901,7 +4364,8 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>令和17年（2035）（令和17年度）</t>
+          <t>令和17年（2035）
+→ 令和17年度（令和18年1月1日現在）</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -3939,7 +4403,7 @@
           <t>＋9.6</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3948,7 +4412,8 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>令和17年（2035）（令和17年度）</t>
+          <t>令和17年（2035）
+→ 令和17年度（令和18年1月1日現在）</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3995,7 +4460,8 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>令和17年（2035）（令和17年度）</t>
+          <t>令和17年（2035）
+→ 令和17年度（令和18年1月1日現在）</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -4033,7 +4499,7 @@
           <t>＋9.6</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4042,7 +4508,8 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>令和22年（2040）（令和22年度）</t>
+          <t>令和22年（2040）
+→ 令和22年度（令和23年1月1日現在）</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -4080,7 +4547,7 @@
           <t>＋21.2</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4089,7 +4556,8 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>令和22年（2040）（令和22年度）</t>
+          <t>令和22年（2040）
+→ 令和22年度（令和23年1月1日現在）</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -4136,7 +4604,8 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>令和22年（2040）（令和22年度）</t>
+          <t>令和22年（2040）
+→ 令和22年度（令和23年1月1日現在）</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -4183,7 +4652,8 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>令和27年（2045）（令和27年度）</t>
+          <t>令和27年（2045）
+→ 令和27年度（令和28年1月1日現在）</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -4221,7 +4691,7 @@
           <t>＋14.8</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4230,7 +4700,8 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>令和27年（2045）（令和27年度）</t>
+          <t>令和27年（2045）
+→ 令和27年度（令和28年1月1日現在）</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -4277,7 +4748,8 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>令和27年（2045）（令和27年度）</t>
+          <t>令和27年（2045）
+→ 令和27年度（令和28年1月1日現在）</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -4315,7 +4787,7 @@
           <t>＋26.4</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4324,7 +4796,8 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>令和32年（2050）（令和32年度）</t>
+          <t>令和32年（2050）
+→ 令和32年度（令和33年1月1日現在）</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -4362,7 +4835,7 @@
           <t>＋10.1</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4371,7 +4844,8 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>令和32年（2050）（令和32年度）</t>
+          <t>令和32年（2050）
+→ 令和32年度（令和33年1月1日現在）</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -4418,7 +4892,8 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>令和32年（2050）（令和32年度）</t>
+          <t>令和32年（2050）
+→ 令和32年度（令和33年1月1日現在）</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -4456,7 +4931,7 @@
           <t>＋12.8</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5112,180 +5587,180 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>総人口</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>27,498</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>26,451</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>25,340</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>24,255</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>23,168</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>22,171</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>9,176</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>9,081</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>8,982</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>9,095</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>8,933</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>8,682</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>5,492</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>5,629</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>5,366</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>5,184</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>5,069</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>5,240</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>85歳以上</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>2,002</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>2,034</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>2,282</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>2,279</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>2,019</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>1,923</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>高齢化率</t>
         </is>
@@ -5454,37 +5929,37 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>65歳以上（案C・採用）</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>9,211</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>9,250</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>9,491</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>9,395</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>9,127</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>総人口は地方創生総合戦略、年齢階級別は住民基本台帳の実績趨勢</t>
         </is>
@@ -5640,7 +6115,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>総人口（受領ファイルのコーホート）</t>
         </is>
@@ -5825,7 +6300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5991,7 +6466,7 @@
           <t>▲200</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>9.2％</t>
         </is>
@@ -6582,12 +7057,12 @@
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>第1号被保険者</t>
         </is>
@@ -6601,7 +7076,7 @@
       <c r="E37" s="20" t="n">
         <v>9430</v>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>男女の65〜69歳から90歳以上までの和</t>
         </is>
@@ -6616,13 +7091,379 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>【4　2つの系列の第1号被保険者数の対比】</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2と3はいずれも社人研推計を補正した第1号被保険者数ですが、総数が一致しません。見える化システムの「総人口と被保険者数の設定」は総数と男女別6階級の両方を求めるため、別の系列から採ると画面の中で計が合わなくなります。→ 確認事項No.174</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2（3）合計</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>3 男女の和</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>（参考）案C</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>9158</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>9153</v>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>▲5</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>9120</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>9120</v>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>±0</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>9,090</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>9117</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>9114</v>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>▲3</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>9116</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>9109</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>▲7</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>9,147</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>9110</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>9102</v>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>▲8</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>9,179</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>9107</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>9094</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>▲13</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>9,213</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>9106</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>9092</v>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>▲14</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>9,211</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>9166</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>9169</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>＋3</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>9,250</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>9375</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>9430</v>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>＋55</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>9,491</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>9270</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>9320</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>＋50</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>9,395</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>8993</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>9016</v>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>＋23</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>9,127</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>差がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>注）差は▲14人から＋55人の幅があり、最も大きいのは令和22年度です。一致するのは令和7年度のみです。
+案Cは当方が令和8年9月30日にお示しした入力値の基礎であり、2・3とは別の系列です（総人口を地方創生総合戦略の水準により置き、年齢階級別の内訳を住民基本台帳の実績趨勢によるもの）。案Cは年度末の値であり、2・3は各年10月1日を基礎とする社人研推計を補正したものであるため、時点も異なります。3つのいずれを採るかは確認事項No.127・No.153・No.174のご判断によります。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
@@ -6834,42 +7675,42 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>26,881</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>25,263</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -6920,7 +7761,7 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>注）**美瑛町には人口ビジョンの年次推計があります。**確認事項No.63では「美瑛町の第3期総合戦略に人口の目標値がない」としていますが、これは総合戦略についてのことであり、人口ビジョンの有無とは別です。計画素案 第6章第1節の注も総合戦略について述べています。
+          <t>注）**美瑛町の人口ビジョンには、2020年・2030年・2040年・2060年の基準年の値があります。**受領ファイルに置かれている1年ごとの値は、この基準年の値を線形に補間したものであり、年次ごとに推計されたものではありません。確認事項No.63では「美瑛町の第3期総合戦略に人口の目標値がない」としていますが、これは総合戦略についてのことであり、人口ビジョンの有無とは別です。計画素案 第6章第1節の注も総合戦略について述べています。
 3町の値の和は2030年26,881人・2040年25,263人で、社人研推計による3町計（R12 25,969人・R22 23,582人）を上回ります。町の計画は施策による上振れを織り込んだ目標であるため、そのまま介護保険の需要推計に用いると給付費を過大に見込む側に働きます。
 案Cは、総人口の水準を総合戦略により置き、年齢階級別の内訳を住民基本台帳の実績趨勢によるものとして組み立てています（計画素案 第2章第1節・第6章第1節）。</t>
         </is>
